--- a/data/results_output.xlsx
+++ b/data/results_output.xlsx
@@ -1,33 +1,470 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec78c8c7a3a47ae9/Desktop/python_work/ferc_scraper/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_F87BF250F13719F9CBB9B9A1118CE596802D62E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0EB9F4F-08E4-4606-A46E-3D10DF14A923}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TEMPLATE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="AD16-16" sheetId="1" r:id="rId1"/>
+    <sheet name="AD24-11" sheetId="2" r:id="rId2"/>
+    <sheet name="AD24-7" sheetId="3" r:id="rId3"/>
+    <sheet name="EL25-44" sheetId="4" r:id="rId4"/>
+    <sheet name="EL25-49" sheetId="5" r:id="rId5"/>
+    <sheet name="ER20-2054" sheetId="6" r:id="rId6"/>
+    <sheet name="RD26-1" sheetId="7" r:id="rId7"/>
+    <sheet name="RD26-2" sheetId="8" r:id="rId8"/>
+    <sheet name="RD26-3" sheetId="9" r:id="rId9"/>
+    <sheet name="RM21-17" sheetId="10" r:id="rId10"/>
+    <sheet name="RM26-4" sheetId="11" r:id="rId11"/>
+    <sheet name="TEMPLATE" sheetId="12" r:id="rId12"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="138">
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Accession No.</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order on Remand re Qualifying Facility Rates and Requirements Implementation Issues Under the Public Utility Regulatory Policies Act of 1978 under RM19-15 et al. </t>
+  </si>
+  <si>
+    <t>03/19/2026</t>
+  </si>
+  <si>
+    <t>Issuance</t>
+  </si>
+  <si>
+    <t>20260319-3063</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260319-3063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comments of the Alliance to Save Energy in support of clear, durable rules that enable responsible large-load integration while preserving reliability, cost causation, and affordability under EL25-49 et al. </t>
+  </si>
+  <si>
+    <t>03/26/2026</t>
+  </si>
+  <si>
+    <t>Submittal</t>
+  </si>
+  <si>
+    <t>20260326-5217</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260326-5217</t>
+  </si>
+  <si>
+    <t>Reply Brief of the Independent Market Monitor in response to PJM Interconnection, L.L.C.’s initial brief filed on 02/23/2026 under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260326-5062</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260326-5062</t>
+  </si>
+  <si>
+    <t>Response Brief of Vistra Corp. under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>03/25/2026</t>
+  </si>
+  <si>
+    <t>20260325-5239</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5239</t>
+  </si>
+  <si>
+    <t>Reply Brief of Constellation Energy Generation, LLC under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260325-5238</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5238</t>
+  </si>
+  <si>
+    <t>Reply Brief of Advanced Energy United and the Solar Energy Industries Association under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260325-5237</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5237</t>
+  </si>
+  <si>
+    <t>Reply Brief of Joint Co-Location Developers and Motion to Intervene Out-of-Time of Calibrant, Convergent, U.S. Energy Storage Coalition, and Versus under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260325-5236</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5236</t>
+  </si>
+  <si>
+    <t>Response Brief of Geronimo Power, LLC under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260325-5235</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5235</t>
+  </si>
+  <si>
+    <t>Responsive Brief of Industrial Customer Organizations and Amtrak under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260325-5234</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5234</t>
+  </si>
+  <si>
+    <t>Reply Brief of Old Dominion Electric Cooperative under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260325-5233</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5233</t>
+  </si>
+  <si>
+    <t>Answer and Motion for Leave to Answer of the Independent Market Monitor for PJM in response to the Initial Brief of PJM Interconnection, L.L.C. filed on 02/23/2026 under EL25-49 et al. Erroneously Filed.</t>
+  </si>
+  <si>
+    <t>20260325-5230</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5230</t>
+  </si>
+  <si>
+    <t>Response of Northern Virginia Electric Cooperative, Inc. to Initial Brief of PJM Interconnection, L.L.C. and to Initial Brief and Joint Responses of the Indicated PJM Transmission Owners to Paper Hearing Questions under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260325-5220</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5220</t>
+  </si>
+  <si>
+    <t>Response of Data Center Coalition to the 02/23/2026 Initial Brief of PJM Interconnection, L.L.C. and the 02/23/2026 Initial Brief of the PJM Transmission Owners re the Order to Show Cause Proceeding under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260325-5208</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5208</t>
+  </si>
+  <si>
+    <t>Joint Response of the Indicated PJM Transmission Owners to PJM Interconnection, L.L.C.’s Initial Brief filed on 02/23/2026 under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260325-5203</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5203</t>
+  </si>
+  <si>
+    <t>Reply Brief and Protest of Enchanted Rock, LLC in response to PJM Interconnection, L.L.C.’s initial brief filed on 02/23/2026 under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260325-5191</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5191</t>
+  </si>
+  <si>
+    <t>Motion for Leave to Answer and Second Answer of Constellation Energy Generation, LLC in response to the Answer filed by PJM Interconnection, L.L.C. under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>03/24/2026</t>
+  </si>
+  <si>
+    <t>20260324-5119</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260324-5119</t>
+  </si>
+  <si>
+    <t>Motion to Intervene Out-of-Time of American Forest &amp; Paper Association under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>03/20/2026</t>
+  </si>
+  <si>
+    <t>20260320-5256</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260320-5256</t>
+  </si>
+  <si>
+    <t>Motion to Intervene Out-of-Time of National Railroad Passenger Corporation ("Amtrak") under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>20260320-5179</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260320-5179</t>
+  </si>
+  <si>
+    <t>Comments of Invenergy Renewables LLC et al. in response to PJM Interconnection, L.L.C.’s Initial Brief in the Order to Show Cause Proceeding and Compliance filing under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>03/16/2026</t>
+  </si>
+  <si>
+    <t>20260316-5254</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260316-5254</t>
+  </si>
+  <si>
+    <t>Motion for Leave to Answer and Answer of PJM Interconnection, L.L.C. to the 02/20/2026 Motion for Leave to Answer and Answer, and the 01/20/2026 Request for Clarification etc. of Constellation Energy Generation under EL25-49 et al.</t>
+  </si>
+  <si>
+    <t>03/09/2026</t>
+  </si>
+  <si>
+    <t>20260309-5267</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260309-5267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notice of Staff Attendance at North American Electric Reliability Corporation Reliability and Security Technical Committee Meetings re Constellation Energy Corporation et al. under EC25-43 et al. </t>
+  </si>
+  <si>
+    <t>03/06/2026</t>
+  </si>
+  <si>
+    <t>20260306-3015</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260306-3015</t>
+  </si>
+  <si>
+    <t>Transcript of the 02/11/2026 Meeting re the Federal and State Current Issues Collaborative under AD24-7.</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>20260303-4000</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260303-4000</t>
+  </si>
+  <si>
+    <t>California Department of Water Resources State Water Project submits request to update the service list under EL24-115 et al.</t>
+  </si>
+  <si>
+    <t>03/17/2026</t>
+  </si>
+  <si>
+    <t>20260317-5220</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260317-5220</t>
+  </si>
+  <si>
+    <t>PJM Interconnection, L.L.C. submits second supplemental Information Report re timeline for stakeholder deliberation on the reliability backstop procurement mechanism under EL25-49.</t>
+  </si>
+  <si>
+    <t>20260309-5165</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260309-5165</t>
+  </si>
+  <si>
+    <t>Motion to Dismiss and Response of Central Maine Power Company to New England States Committee on Electricity, Inc.'s 02/09/2026 Formal Challenge under ER20-2054.</t>
+  </si>
+  <si>
+    <t>03/23/2026</t>
+  </si>
+  <si>
+    <t>20260323-5243</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260323-5243</t>
+  </si>
+  <si>
+    <t>20260323-5242</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260323-5242</t>
+  </si>
+  <si>
+    <t>(doc-less) Out-of-Time Motion to Intervene of WIRES under ER20-2054.</t>
+  </si>
+  <si>
+    <t>20260319-5213</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260319-5213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Errata to the 02/18/2026 Combined Notice of Filings #1; correcting the applicant's name re New England States Committee on Electricity, Inc. under ER20-2054. For notice see accession number 20260218-3070. </t>
+  </si>
+  <si>
+    <t>03/12/2026</t>
+  </si>
+  <si>
+    <t>20260312-3061</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260312-3061</t>
+  </si>
+  <si>
+    <t>Motion for Leave to Answer and Limited Answer of New England Power Company d/b/a National Grid to the Maine Office of Public Advocate's 02/17/2026 Motion for Leave to Answer and Answer under ER20-2054.</t>
+  </si>
+  <si>
+    <t>03/04/2026</t>
+  </si>
+  <si>
+    <t>20260304-5185</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260304-5185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notice of Staff Attendance at North American Electric Reliability Corporation Operational Studies Drafting Teams Meetings and Standards Committee Meeting re North American Electric Reliability Corporation under RD26-1 et al. </t>
+  </si>
+  <si>
+    <t>20260304-3030</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260304-3030</t>
+  </si>
+  <si>
+    <t>Comments of the New York Transmission Owners in Support of New York Independent System Operator, Inc.'s 03/20/2026 Motion for Extension of Time under RM21-17.</t>
+  </si>
+  <si>
+    <t>03/27/2026</t>
+  </si>
+  <si>
+    <t>20260327-5066</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260327-5066</t>
+  </si>
+  <si>
+    <t>Answer of the New York State Public Service Commission in support of 03/20/2026 Motion for a 60-day extension of the due date to submit compliance filing et al. filed by New York Independent System Operator, Inc. under RM21-17.</t>
+  </si>
+  <si>
+    <t>20260325-5134</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260325-5134</t>
+  </si>
+  <si>
+    <t>New York Independent System Operator, Inc. submits request for extension of time until 06/29/2026 to submit Compliance Filing and request for expedited action under RM21-17.</t>
+  </si>
+  <si>
+    <t>20260320-5207</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260320-5207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comment of Alexandre Figueras in Docket(s)/Project(s) RM26-4-000
+Submission Date: 3/26/2026
+</t>
+  </si>
+  <si>
+    <t>20260327-5004</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260327-5004</t>
+  </si>
+  <si>
+    <t>Kansas Corporation Commission submits request to update the service list under RM26-4 et al.</t>
+  </si>
+  <si>
+    <t>20260324-5118</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260324-5118</t>
+  </si>
+  <si>
+    <t>Comments of North American Electric Reliability Corporation providing supplement re activities over the last quarter et al. re Interconnection of Large Loads to the Interstate Transmission System under RM26-4.</t>
+  </si>
+  <si>
+    <t>20260320-5091</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260320-5091</t>
+  </si>
+  <si>
+    <t>Supplemental Comments of Entergy Services, LLC, et al. re the Interconnection of Large Loads to the Interstate Transmission System under RM26-4.</t>
+  </si>
+  <si>
+    <t>20260316-5144</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260316-5144</t>
+  </si>
+  <si>
+    <t>Comments of Edison Electric Institute in response to FERC's Notice of Proposed Rulemaking related to Large Load Projects and State Tariffs under RM26-4.</t>
+  </si>
+  <si>
+    <t>20260312-5096</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260312-5096</t>
+  </si>
+  <si>
+    <t>Consumers Energy Company submits request to update the service list under EL25-90 et al.</t>
+  </si>
+  <si>
+    <t>03/11/2026</t>
+  </si>
+  <si>
+    <t>20260311-5073</t>
+  </si>
+  <si>
+    <t>https://elibrary.ferc.gov/eLibrary/filelist?accession_number=20260311-5073</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +483,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -385,42 +763,1436 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="8.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Accession No.</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="42.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/results_output.xlsx
+++ b/data/results_output.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="TEMPLATE" sheetId="1" state="visible" r:id="rId1"/>

--- a/data/results_output.xlsx
+++ b/data/results_output.xlsx
@@ -1,33 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec78c8c7a3a47ae9/Desktop/python_work/docket-scraper/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_41A15231CD28458868794A3869BC6E393260246D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8EF2C58-69BB-448D-AA06-324BD1E46093}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TEMPLATE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TEMPLATE" sheetId="10" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Accession No.</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,80 +71,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -385,39 +351,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Accession No.</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
